--- a/backend/docs/TRA-DEC.xlsx
+++ b/backend/docs/TRA-DEC.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26626"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Brian\Documents\planosperu-app\backend\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell Latitude\Documents\Projects\planos-react-app\backend\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDB8428C-A660-4A1F-9F40-F4B6536BFF3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E403C796-0EE6-44A9-8CC3-FEAC49C97C67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{03CDC904-23BA-49AE-AA6F-5DD301F77889}"/>
   </bookViews>
@@ -806,7 +806,295 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -816,10 +1104,6 @@
       <alignment horizontal="right" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
       <protection locked="0"/>
@@ -843,296 +1127,12 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+    <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1575,24 +1575,38 @@
             <a:defRPr sz="1000"/>
           </a:pPr>
           <a:r>
-            <a:rPr lang="es-PE" sz="900" b="1" i="0" u="none" strike="noStrike" baseline="0">
+            <a:rPr kumimoji="0" lang="es-PE" sz="900" b="1" i="0" u="none" strike="noStrike" kern="0" cap="none" spc="0" normalizeH="0" baseline="0" noProof="0">
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
               <a:solidFill>
                 <a:srgbClr val="000000"/>
               </a:solidFill>
+              <a:effectLst/>
+              <a:uLnTx/>
+              <a:uFillTx/>
               <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+              <a:ea typeface="+mn-ea"/>
               <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
             </a:rPr>
             <a:t>        </a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="es-PE" sz="900" b="1" i="0" u="none" strike="noStrike" baseline="0">
+            <a:rPr kumimoji="0" lang="es-PE" sz="900" b="1" i="0" u="none" strike="noStrike" kern="0" cap="none" spc="0" normalizeH="0" baseline="0" noProof="0">
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
               <a:solidFill>
                 <a:srgbClr val="002060"/>
               </a:solidFill>
+              <a:effectLst/>
+              <a:uLnTx/>
+              <a:uFillTx/>
               <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+              <a:ea typeface="+mn-ea"/>
               <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
             </a:rPr>
-            <a:t>CTA BCP CUENTA CORRIENTE SOLES: 191-7674171-0-77   </a:t>
+            <a:t>CTA BCP CUENTA CORRIENTE SOLES: 191-7674171-0-77  CCI: 00219100767417107756</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -1614,26 +1628,21 @@
             <a:defRPr sz="1000"/>
           </a:pPr>
           <a:r>
-            <a:rPr lang="es-PE" sz="900" b="1" i="0" baseline="0">
+            <a:rPr kumimoji="0" lang="es-PE" sz="900" b="1" i="0" u="none" strike="noStrike" kern="0" cap="none" spc="0" normalizeH="0" baseline="0" noProof="0">
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
               <a:solidFill>
                 <a:srgbClr val="002060"/>
               </a:solidFill>
               <a:effectLst/>
+              <a:uLnTx/>
+              <a:uFillTx/>
               <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
             </a:rPr>
-            <a:t>CCI: 00219100767417107756 T</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="es-PE" sz="900" b="1" i="0" u="none" strike="noStrike" baseline="0">
-              <a:solidFill>
-                <a:srgbClr val="002060"/>
-              </a:solidFill>
-              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>itular Ing. Atapaucar Bardales Richard</a:t>
+            <a:t>Cuenta BBVA: Número de cuenta: 0011-0814-0278938730   CCI: 0118140002789387</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -1655,49 +1664,119 @@
             <a:defRPr sz="1000"/>
           </a:pPr>
           <a:r>
-            <a:rPr lang="es-PE" sz="900" b="1" i="0" u="none" strike="noStrike" baseline="0">
+            <a:rPr kumimoji="0" lang="es-PE" sz="900" b="1" i="0" u="none" strike="noStrike" kern="0" cap="none" spc="0" normalizeH="0" baseline="0" noProof="0">
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
               <a:solidFill>
                 <a:srgbClr val="002060"/>
               </a:solidFill>
+              <a:effectLst/>
+              <a:uLnTx/>
+              <a:uFillTx/>
               <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+              <a:ea typeface="+mn-ea"/>
               <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
             </a:rPr>
-            <a:t>Se aceptan todo tipo de Tarjetas de Credito</a:t>
+            <a:t>Titular Ing. Atapaucar Bardales Richard. Se aceptan todo tipo de Tarjetas de Credito</a:t>
           </a:r>
         </a:p>
         <a:p>
-          <a:pPr algn="l" rtl="0">
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
             <a:defRPr sz="1000"/>
           </a:pPr>
-          <a:endParaRPr lang="es-PE" sz="1150" b="1" i="0" u="none" strike="noStrike" baseline="0">
+          <a:endParaRPr kumimoji="0" lang="es-PE" sz="1150" b="1" i="0" u="none" strike="noStrike" kern="0" cap="none" spc="0" normalizeH="0" baseline="0" noProof="0">
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
             <a:solidFill>
               <a:srgbClr val="FFFFFF"/>
             </a:solidFill>
+            <a:effectLst/>
+            <a:uLnTx/>
+            <a:uFillTx/>
             <a:latin typeface="Times New Roman"/>
+            <a:ea typeface="+mn-ea"/>
             <a:cs typeface="Times New Roman"/>
           </a:endParaRPr>
         </a:p>
         <a:p>
-          <a:pPr algn="l" rtl="0">
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
             <a:defRPr sz="1000"/>
           </a:pPr>
-          <a:endParaRPr lang="es-PE" sz="1100" b="0" i="0" u="none" strike="noStrike" baseline="0">
+          <a:endParaRPr kumimoji="0" lang="es-PE" sz="1100" b="0" i="0" u="none" strike="noStrike" kern="0" cap="none" spc="0" normalizeH="0" baseline="0" noProof="0">
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
             <a:solidFill>
               <a:srgbClr val="000000"/>
             </a:solidFill>
+            <a:effectLst/>
+            <a:uLnTx/>
+            <a:uFillTx/>
             <a:latin typeface="Times New Roman"/>
+            <a:ea typeface="+mn-ea"/>
             <a:cs typeface="Times New Roman"/>
           </a:endParaRPr>
         </a:p>
         <a:p>
-          <a:pPr algn="l" rtl="0">
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
             <a:defRPr sz="1000"/>
           </a:pPr>
-          <a:endParaRPr lang="es-PE" sz="1100" b="0" i="0" u="none" strike="noStrike" baseline="0">
+          <a:endParaRPr kumimoji="0" lang="es-PE" sz="1100" b="0" i="0" u="none" strike="noStrike" kern="0" cap="none" spc="0" normalizeH="0" baseline="0" noProof="0">
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
             <a:solidFill>
               <a:srgbClr val="000000"/>
             </a:solidFill>
+            <a:effectLst/>
+            <a:uLnTx/>
+            <a:uFillTx/>
             <a:latin typeface="Times New Roman"/>
+            <a:ea typeface="+mn-ea"/>
             <a:cs typeface="Times New Roman"/>
           </a:endParaRPr>
         </a:p>
@@ -1797,9 +1876,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1837,7 +1916,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1943,7 +2022,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2085,7 +2164,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2098,7 +2177,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A3:H81"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="4" max="4" width="14.28515625" customWidth="1"/>
@@ -2117,86 +2196,86 @@
       <c r="C4" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="126" t="s">
+      <c r="D4" s="44" t="s">
         <v>98</v>
       </c>
-      <c r="E4" s="126"/>
-      <c r="F4" s="126"/>
+      <c r="E4" s="44"/>
+      <c r="F4" s="44"/>
       <c r="G4" s="2"/>
     </row>
     <row r="5" spans="1:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C5" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="127" t="s">
+      <c r="D5" s="45" t="s">
         <v>99</v>
       </c>
-      <c r="E5" s="127"/>
-      <c r="F5" s="127"/>
+      <c r="E5" s="45"/>
+      <c r="F5" s="45"/>
       <c r="G5" s="3"/>
     </row>
     <row r="6" spans="1:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C6" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="D6" s="128" t="s">
+      <c r="D6" s="46" t="s">
         <v>97</v>
       </c>
-      <c r="E6" s="128"/>
-      <c r="F6" s="128"/>
+      <c r="E6" s="46"/>
+      <c r="F6" s="46"/>
       <c r="G6" s="4"/>
     </row>
     <row r="7" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C7" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="D7" s="129" t="s">
+      <c r="D7" s="47" t="s">
         <v>96</v>
       </c>
-      <c r="E7" s="129"/>
-      <c r="F7" s="129"/>
+      <c r="E7" s="47"/>
+      <c r="F7" s="47"/>
       <c r="G7" s="4"/>
     </row>
     <row r="8" spans="1:8" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="130"/>
-      <c r="B8" s="130"/>
-      <c r="C8" s="130"/>
-      <c r="D8" s="130"/>
-      <c r="E8" s="130"/>
-      <c r="F8" s="130"/>
-      <c r="G8" s="130"/>
-      <c r="H8" s="130"/>
+      <c r="A8" s="48"/>
+      <c r="B8" s="48"/>
+      <c r="C8" s="48"/>
+      <c r="D8" s="48"/>
+      <c r="E8" s="48"/>
+      <c r="F8" s="48"/>
+      <c r="G8" s="48"/>
+      <c r="H8" s="48"/>
     </row>
     <row r="9" spans="1:8" s="5" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="125" t="s">
+      <c r="B9" s="43" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="125"/>
-      <c r="D9" s="125"/>
-      <c r="E9" s="125"/>
-      <c r="F9" s="125"/>
-      <c r="G9" s="125"/>
+      <c r="C9" s="43"/>
+      <c r="D9" s="43"/>
+      <c r="E9" s="43"/>
+      <c r="F9" s="43"/>
+      <c r="G9" s="43"/>
       <c r="H9" s="6"/>
     </row>
     <row r="10" spans="1:8" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="125"/>
-      <c r="C10" s="125"/>
-      <c r="D10" s="125"/>
-      <c r="E10" s="125"/>
-      <c r="F10" s="125"/>
-      <c r="G10" s="125"/>
+      <c r="B10" s="43"/>
+      <c r="C10" s="43"/>
+      <c r="D10" s="43"/>
+      <c r="E10" s="43"/>
+      <c r="F10" s="43"/>
+      <c r="G10" s="43"/>
       <c r="H10" s="6"/>
     </row>
     <row r="11" spans="1:8" s="11" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B11" s="116" t="s">
+      <c r="B11" s="52" t="s">
         <v>7</v>
       </c>
-      <c r="C11" s="116"/>
-      <c r="D11" s="116"/>
-      <c r="E11" s="116"/>
+      <c r="C11" s="52"/>
+      <c r="D11" s="52"/>
+      <c r="E11" s="52"/>
       <c r="F11" s="8" t="s">
         <v>8</v>
       </c>
@@ -2205,22 +2284,22 @@
     </row>
     <row r="12" spans="1:8" s="11" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="7"/>
-      <c r="B12" s="116"/>
-      <c r="C12" s="116"/>
-      <c r="D12" s="116"/>
-      <c r="E12" s="116"/>
-      <c r="F12" s="116"/>
-      <c r="G12" s="116"/>
+      <c r="B12" s="52"/>
+      <c r="C12" s="52"/>
+      <c r="D12" s="52"/>
+      <c r="E12" s="52"/>
+      <c r="F12" s="52"/>
+      <c r="G12" s="52"/>
       <c r="H12" s="10"/>
     </row>
     <row r="13" spans="1:8" s="11" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="12"/>
-      <c r="B13" s="116"/>
-      <c r="C13" s="116"/>
-      <c r="D13" s="116"/>
-      <c r="E13" s="116"/>
-      <c r="F13" s="116"/>
-      <c r="G13" s="116"/>
+      <c r="B13" s="52"/>
+      <c r="C13" s="52"/>
+      <c r="D13" s="52"/>
+      <c r="E13" s="52"/>
+      <c r="F13" s="52"/>
+      <c r="G13" s="52"/>
       <c r="H13" s="10"/>
     </row>
     <row r="14" spans="1:8" s="11" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
@@ -2245,10 +2324,10 @@
       <c r="A15" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="B15" s="116"/>
-      <c r="C15" s="116"/>
-      <c r="D15" s="116"/>
-      <c r="E15" s="116"/>
+      <c r="B15" s="52"/>
+      <c r="C15" s="52"/>
+      <c r="D15" s="52"/>
+      <c r="E15" s="52"/>
       <c r="F15" s="13" t="s">
         <v>13</v>
       </c>
@@ -2257,10 +2336,10 @@
     </row>
     <row r="16" spans="1:8" s="11" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="12"/>
-      <c r="B16" s="117"/>
-      <c r="C16" s="117"/>
-      <c r="D16" s="117"/>
-      <c r="E16" s="117"/>
+      <c r="B16" s="53"/>
+      <c r="C16" s="53"/>
+      <c r="D16" s="53"/>
+      <c r="E16" s="53"/>
       <c r="F16" s="13" t="s">
         <v>14</v>
       </c>
@@ -2271,14 +2350,14 @@
       <c r="A17" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="B17" s="116"/>
-      <c r="C17" s="116"/>
+      <c r="B17" s="52"/>
+      <c r="C17" s="52"/>
       <c r="D17" s="18" t="s">
         <v>16</v>
       </c>
       <c r="E17" s="19">
         <f ca="1">TODAY()</f>
-        <v>45870</v>
+        <v>45973</v>
       </c>
       <c r="F17" s="15"/>
       <c r="G17" s="15"/>
@@ -2286,443 +2365,443 @@
     </row>
     <row r="18" spans="1:8" s="11" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="20"/>
-      <c r="B18" s="118"/>
-      <c r="C18" s="118"/>
-      <c r="D18" s="118"/>
-      <c r="E18" s="118"/>
-      <c r="F18" s="118"/>
-      <c r="G18" s="118"/>
+      <c r="B18" s="54"/>
+      <c r="C18" s="54"/>
+      <c r="D18" s="54"/>
+      <c r="E18" s="54"/>
+      <c r="F18" s="54"/>
+      <c r="G18" s="54"/>
       <c r="H18" s="20"/>
     </row>
     <row r="19" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="21"/>
-      <c r="B19" s="119" t="s">
+      <c r="B19" s="55" t="s">
         <v>17</v>
       </c>
-      <c r="C19" s="120"/>
-      <c r="D19" s="121"/>
-      <c r="E19" s="122"/>
-      <c r="F19" s="122"/>
-      <c r="G19" s="122"/>
+      <c r="C19" s="56"/>
+      <c r="D19" s="57"/>
+      <c r="E19" s="58"/>
+      <c r="F19" s="58"/>
+      <c r="G19" s="58"/>
       <c r="H19" s="22"/>
     </row>
     <row r="20" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="10"/>
-      <c r="B20" s="85" t="s">
+      <c r="B20" s="59" t="s">
         <v>18</v>
       </c>
-      <c r="C20" s="86"/>
-      <c r="D20" s="87"/>
-      <c r="E20" s="123" t="s">
+      <c r="C20" s="60"/>
+      <c r="D20" s="61"/>
+      <c r="E20" s="62" t="s">
         <v>19</v>
       </c>
-      <c r="F20" s="123"/>
-      <c r="G20" s="124"/>
+      <c r="F20" s="62"/>
+      <c r="G20" s="63"/>
       <c r="H20" s="10"/>
     </row>
     <row r="21" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="10"/>
-      <c r="B21" s="108" t="s">
+      <c r="B21" s="49" t="s">
         <v>20</v>
       </c>
-      <c r="C21" s="109"/>
-      <c r="D21" s="110"/>
-      <c r="E21" s="109" t="s">
+      <c r="C21" s="50"/>
+      <c r="D21" s="51"/>
+      <c r="E21" s="50" t="s">
         <v>21</v>
       </c>
-      <c r="F21" s="109"/>
-      <c r="G21" s="110"/>
+      <c r="F21" s="50"/>
+      <c r="G21" s="51"/>
       <c r="H21" s="10"/>
     </row>
     <row r="22" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="10"/>
-      <c r="B22" s="57" t="s">
+      <c r="B22" s="64" t="s">
         <v>22</v>
       </c>
-      <c r="C22" s="58"/>
-      <c r="D22" s="58"/>
-      <c r="E22" s="114"/>
-      <c r="F22" s="114"/>
-      <c r="G22" s="115"/>
+      <c r="C22" s="65"/>
+      <c r="D22" s="65"/>
+      <c r="E22" s="66"/>
+      <c r="F22" s="66"/>
+      <c r="G22" s="67"/>
       <c r="H22" s="10"/>
     </row>
     <row r="23" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="10"/>
-      <c r="B23" s="108" t="s">
+      <c r="B23" s="49" t="s">
         <v>23</v>
       </c>
-      <c r="C23" s="109"/>
-      <c r="D23" s="110"/>
-      <c r="E23" s="108" t="s">
+      <c r="C23" s="50"/>
+      <c r="D23" s="51"/>
+      <c r="E23" s="49" t="s">
         <v>24</v>
       </c>
-      <c r="F23" s="109"/>
-      <c r="G23" s="110"/>
+      <c r="F23" s="50"/>
+      <c r="G23" s="51"/>
       <c r="H23" s="10"/>
     </row>
     <row r="24" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="10"/>
-      <c r="B24" s="85" t="s">
+      <c r="B24" s="59" t="s">
         <v>25</v>
       </c>
-      <c r="C24" s="86"/>
-      <c r="D24" s="87"/>
-      <c r="E24" s="108" t="s">
+      <c r="C24" s="60"/>
+      <c r="D24" s="61"/>
+      <c r="E24" s="49" t="s">
         <v>26</v>
       </c>
-      <c r="F24" s="109"/>
-      <c r="G24" s="110"/>
+      <c r="F24" s="50"/>
+      <c r="G24" s="51"/>
       <c r="H24" s="10"/>
     </row>
     <row r="25" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="24"/>
-      <c r="B25" s="108" t="s">
+      <c r="B25" s="49" t="s">
         <v>27</v>
       </c>
-      <c r="C25" s="109"/>
-      <c r="D25" s="110"/>
-      <c r="E25" s="85" t="s">
+      <c r="C25" s="50"/>
+      <c r="D25" s="51"/>
+      <c r="E25" s="59" t="s">
         <v>28</v>
       </c>
-      <c r="F25" s="86"/>
-      <c r="G25" s="87"/>
+      <c r="F25" s="60"/>
+      <c r="G25" s="61"/>
       <c r="H25" s="10"/>
     </row>
     <row r="26" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="25"/>
-      <c r="B26" s="108" t="s">
+      <c r="B26" s="49" t="s">
         <v>29</v>
       </c>
-      <c r="C26" s="109"/>
-      <c r="D26" s="110"/>
-      <c r="E26" s="108" t="s">
+      <c r="C26" s="50"/>
+      <c r="D26" s="51"/>
+      <c r="E26" s="49" t="s">
         <v>30</v>
       </c>
-      <c r="F26" s="109"/>
-      <c r="G26" s="110"/>
+      <c r="F26" s="50"/>
+      <c r="G26" s="51"/>
       <c r="H26" s="10"/>
     </row>
     <row r="27" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="25"/>
-      <c r="B27" s="111" t="s">
+      <c r="B27" s="68" t="s">
         <v>31</v>
       </c>
-      <c r="C27" s="112"/>
-      <c r="D27" s="113"/>
-      <c r="E27" s="108" t="s">
+      <c r="C27" s="69"/>
+      <c r="D27" s="70"/>
+      <c r="E27" s="49" t="s">
         <v>32</v>
       </c>
-      <c r="F27" s="109"/>
-      <c r="G27" s="110"/>
+      <c r="F27" s="50"/>
+      <c r="G27" s="51"/>
       <c r="H27" s="10"/>
     </row>
     <row r="28" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="25"/>
-      <c r="B28" s="94" t="s">
+      <c r="B28" s="77" t="s">
         <v>33</v>
       </c>
-      <c r="C28" s="95"/>
-      <c r="D28" s="96"/>
-      <c r="E28" s="97" t="s">
+      <c r="C28" s="78"/>
+      <c r="D28" s="79"/>
+      <c r="E28" s="80" t="s">
         <v>34</v>
       </c>
-      <c r="F28" s="98"/>
-      <c r="G28" s="99"/>
+      <c r="F28" s="81"/>
+      <c r="G28" s="82"/>
       <c r="H28" s="10"/>
     </row>
     <row r="29" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="25"/>
-      <c r="B29" s="57" t="s">
+      <c r="B29" s="64" t="s">
         <v>35</v>
       </c>
-      <c r="C29" s="58"/>
-      <c r="D29" s="58"/>
-      <c r="E29" s="100"/>
-      <c r="F29" s="100"/>
-      <c r="G29" s="101"/>
+      <c r="C29" s="65"/>
+      <c r="D29" s="65"/>
+      <c r="E29" s="83"/>
+      <c r="F29" s="83"/>
+      <c r="G29" s="84"/>
       <c r="H29" s="10"/>
     </row>
     <row r="30" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="26"/>
-      <c r="B30" s="102" t="s">
+      <c r="B30" s="85" t="s">
         <v>36</v>
       </c>
-      <c r="C30" s="103"/>
-      <c r="D30" s="104"/>
-      <c r="E30" s="102" t="s">
+      <c r="C30" s="86"/>
+      <c r="D30" s="87"/>
+      <c r="E30" s="85" t="s">
         <v>37</v>
       </c>
-      <c r="F30" s="103"/>
-      <c r="G30" s="104"/>
+      <c r="F30" s="86"/>
+      <c r="G30" s="87"/>
       <c r="H30" s="10"/>
     </row>
     <row r="31" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="26"/>
-      <c r="B31" s="54" t="s">
+      <c r="B31" s="74" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="55"/>
-      <c r="D31" s="56"/>
-      <c r="E31" s="54" t="s">
+      <c r="C31" s="75"/>
+      <c r="D31" s="76"/>
+      <c r="E31" s="74" t="s">
         <v>39</v>
       </c>
-      <c r="F31" s="55"/>
-      <c r="G31" s="56"/>
+      <c r="F31" s="75"/>
+      <c r="G31" s="76"/>
       <c r="H31" s="10"/>
     </row>
     <row r="32" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="27"/>
-      <c r="B32" s="105" t="s">
+      <c r="B32" s="88" t="s">
         <v>40</v>
       </c>
-      <c r="C32" s="106"/>
-      <c r="D32" s="107"/>
-      <c r="E32" s="54" t="s">
+      <c r="C32" s="89"/>
+      <c r="D32" s="90"/>
+      <c r="E32" s="74" t="s">
         <v>41</v>
       </c>
-      <c r="F32" s="55"/>
-      <c r="G32" s="56"/>
+      <c r="F32" s="75"/>
+      <c r="G32" s="76"/>
       <c r="H32" s="10"/>
     </row>
     <row r="33" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="10"/>
-      <c r="B33" s="105"/>
-      <c r="C33" s="106"/>
-      <c r="D33" s="107"/>
-      <c r="E33" s="54" t="s">
+      <c r="B33" s="88"/>
+      <c r="C33" s="89"/>
+      <c r="D33" s="90"/>
+      <c r="E33" s="74" t="s">
         <v>42</v>
       </c>
-      <c r="F33" s="55"/>
-      <c r="G33" s="56"/>
+      <c r="F33" s="75"/>
+      <c r="G33" s="76"/>
       <c r="H33" s="10"/>
     </row>
     <row r="34" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="10"/>
-      <c r="B34" s="54" t="s">
+      <c r="B34" s="74" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="55"/>
-      <c r="D34" s="56"/>
-      <c r="E34" s="54" t="s">
+      <c r="C34" s="75"/>
+      <c r="D34" s="76"/>
+      <c r="E34" s="74" t="s">
         <v>44</v>
       </c>
-      <c r="F34" s="55"/>
-      <c r="G34" s="56"/>
+      <c r="F34" s="75"/>
+      <c r="G34" s="76"/>
       <c r="H34" s="10"/>
     </row>
     <row r="35" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="10"/>
-      <c r="B35" s="91" t="s">
+      <c r="B35" s="71" t="s">
         <v>45</v>
       </c>
-      <c r="C35" s="92"/>
-      <c r="D35" s="93"/>
-      <c r="E35" s="54" t="s">
+      <c r="C35" s="72"/>
+      <c r="D35" s="73"/>
+      <c r="E35" s="74" t="s">
         <v>46</v>
       </c>
-      <c r="F35" s="55"/>
-      <c r="G35" s="56"/>
+      <c r="F35" s="75"/>
+      <c r="G35" s="76"/>
       <c r="H35" s="10"/>
     </row>
     <row r="36" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="10"/>
-      <c r="B36" s="91"/>
-      <c r="C36" s="92"/>
-      <c r="D36" s="93"/>
-      <c r="E36" s="54" t="s">
+      <c r="B36" s="71"/>
+      <c r="C36" s="72"/>
+      <c r="D36" s="73"/>
+      <c r="E36" s="74" t="s">
         <v>47</v>
       </c>
-      <c r="F36" s="55"/>
-      <c r="G36" s="56"/>
+      <c r="F36" s="75"/>
+      <c r="G36" s="76"/>
       <c r="H36" s="10"/>
     </row>
     <row r="37" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="10"/>
-      <c r="B37" s="85" t="s">
+      <c r="B37" s="59" t="s">
         <v>48</v>
       </c>
-      <c r="C37" s="86"/>
-      <c r="D37" s="87"/>
-      <c r="E37" s="79" t="s">
+      <c r="C37" s="60"/>
+      <c r="D37" s="61"/>
+      <c r="E37" s="91" t="s">
         <v>49</v>
       </c>
-      <c r="F37" s="80"/>
-      <c r="G37" s="81"/>
+      <c r="F37" s="92"/>
+      <c r="G37" s="93"/>
       <c r="H37" s="10"/>
     </row>
     <row r="38" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="10"/>
-      <c r="B38" s="54" t="s">
+      <c r="B38" s="74" t="s">
         <v>50</v>
       </c>
-      <c r="C38" s="55"/>
-      <c r="D38" s="56"/>
-      <c r="E38" s="79" t="s">
+      <c r="C38" s="75"/>
+      <c r="D38" s="76"/>
+      <c r="E38" s="91" t="s">
         <v>51</v>
       </c>
-      <c r="F38" s="80"/>
-      <c r="G38" s="81"/>
+      <c r="F38" s="92"/>
+      <c r="G38" s="93"/>
       <c r="H38" s="10"/>
     </row>
     <row r="39" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="10"/>
-      <c r="B39" s="54" t="s">
+      <c r="B39" s="74" t="s">
         <v>52</v>
       </c>
-      <c r="C39" s="55"/>
-      <c r="D39" s="56"/>
-      <c r="E39" s="88" t="s">
+      <c r="C39" s="75"/>
+      <c r="D39" s="76"/>
+      <c r="E39" s="94" t="s">
         <v>53</v>
       </c>
-      <c r="F39" s="89"/>
-      <c r="G39" s="90"/>
+      <c r="F39" s="95"/>
+      <c r="G39" s="96"/>
       <c r="H39" s="10"/>
     </row>
     <row r="40" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="10"/>
-      <c r="B40" s="54" t="s">
+      <c r="B40" s="74" t="s">
         <v>54</v>
       </c>
-      <c r="C40" s="55"/>
-      <c r="D40" s="56"/>
-      <c r="E40" s="76" t="s">
+      <c r="C40" s="75"/>
+      <c r="D40" s="76"/>
+      <c r="E40" s="97" t="s">
         <v>55</v>
       </c>
-      <c r="F40" s="77"/>
-      <c r="G40" s="78"/>
+      <c r="F40" s="98"/>
+      <c r="G40" s="99"/>
       <c r="H40" s="10"/>
     </row>
     <row r="41" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="10"/>
-      <c r="B41" s="54" t="s">
+      <c r="B41" s="74" t="s">
         <v>56</v>
       </c>
-      <c r="C41" s="55"/>
-      <c r="D41" s="56"/>
-      <c r="E41" s="79" t="s">
+      <c r="C41" s="75"/>
+      <c r="D41" s="76"/>
+      <c r="E41" s="91" t="s">
         <v>57</v>
       </c>
-      <c r="F41" s="80"/>
-      <c r="G41" s="81"/>
+      <c r="F41" s="92"/>
+      <c r="G41" s="93"/>
       <c r="H41" s="10"/>
     </row>
     <row r="42" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="10"/>
-      <c r="B42" s="54" t="s">
+      <c r="B42" s="74" t="s">
         <v>58</v>
       </c>
-      <c r="C42" s="55"/>
-      <c r="D42" s="56"/>
-      <c r="E42" s="82" t="s">
+      <c r="C42" s="75"/>
+      <c r="D42" s="76"/>
+      <c r="E42" s="100" t="s">
         <v>59</v>
       </c>
-      <c r="F42" s="83"/>
-      <c r="G42" s="84"/>
+      <c r="F42" s="101"/>
+      <c r="G42" s="102"/>
       <c r="H42" s="10"/>
     </row>
     <row r="43" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="10"/>
-      <c r="B43" s="54" t="s">
+      <c r="B43" s="74" t="s">
         <v>60</v>
       </c>
-      <c r="C43" s="55"/>
-      <c r="D43" s="56"/>
+      <c r="C43" s="75"/>
+      <c r="D43" s="76"/>
       <c r="E43" s="28"/>
       <c r="F43" s="29"/>
       <c r="G43" s="30"/>
       <c r="H43" s="10"/>
     </row>
     <row r="44" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B44" s="57" t="s">
+      <c r="B44" s="64" t="s">
         <v>61</v>
       </c>
-      <c r="C44" s="58"/>
-      <c r="D44" s="58"/>
-      <c r="E44" s="58"/>
-      <c r="F44" s="58"/>
-      <c r="G44" s="59"/>
+      <c r="C44" s="65"/>
+      <c r="D44" s="65"/>
+      <c r="E44" s="65"/>
+      <c r="F44" s="65"/>
+      <c r="G44" s="104"/>
       <c r="H44" s="10"/>
     </row>
     <row r="45" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="10"/>
-      <c r="B45" s="60" t="s">
+      <c r="B45" s="105" t="s">
         <v>62</v>
       </c>
-      <c r="C45" s="61"/>
-      <c r="D45" s="62"/>
-      <c r="E45" s="60" t="s">
+      <c r="C45" s="106"/>
+      <c r="D45" s="107"/>
+      <c r="E45" s="105" t="s">
         <v>63</v>
       </c>
-      <c r="F45" s="61"/>
-      <c r="G45" s="62"/>
+      <c r="F45" s="106"/>
+      <c r="G45" s="107"/>
       <c r="H45" s="10"/>
     </row>
     <row r="46" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="10"/>
-      <c r="B46" s="63"/>
-      <c r="C46" s="64"/>
-      <c r="D46" s="65"/>
-      <c r="E46" s="63"/>
-      <c r="F46" s="64"/>
-      <c r="G46" s="65"/>
+      <c r="B46" s="108"/>
+      <c r="C46" s="109"/>
+      <c r="D46" s="110"/>
+      <c r="E46" s="108"/>
+      <c r="F46" s="109"/>
+      <c r="G46" s="110"/>
       <c r="H46" s="10"/>
     </row>
     <row r="47" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="10"/>
-      <c r="B47" s="63"/>
-      <c r="C47" s="64"/>
-      <c r="D47" s="65"/>
-      <c r="E47" s="63" t="s">
+      <c r="B47" s="108"/>
+      <c r="C47" s="109"/>
+      <c r="D47" s="110"/>
+      <c r="E47" s="108" t="s">
         <v>64</v>
       </c>
-      <c r="F47" s="64"/>
-      <c r="G47" s="65"/>
+      <c r="F47" s="109"/>
+      <c r="G47" s="110"/>
       <c r="H47" s="10"/>
     </row>
     <row r="48" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="10"/>
-      <c r="B48" s="63" t="s">
+      <c r="B48" s="108" t="s">
         <v>65</v>
       </c>
-      <c r="C48" s="64"/>
-      <c r="D48" s="65"/>
-      <c r="E48" s="63"/>
-      <c r="F48" s="64"/>
-      <c r="G48" s="65"/>
+      <c r="C48" s="109"/>
+      <c r="D48" s="110"/>
+      <c r="E48" s="108"/>
+      <c r="F48" s="109"/>
+      <c r="G48" s="110"/>
       <c r="H48" s="10"/>
     </row>
     <row r="49" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="10"/>
-      <c r="B49" s="63"/>
-      <c r="C49" s="64"/>
-      <c r="D49" s="65"/>
-      <c r="E49" s="63" t="s">
+      <c r="B49" s="108"/>
+      <c r="C49" s="109"/>
+      <c r="D49" s="110"/>
+      <c r="E49" s="108" t="s">
         <v>66</v>
       </c>
-      <c r="F49" s="64"/>
-      <c r="G49" s="65"/>
+      <c r="F49" s="109"/>
+      <c r="G49" s="110"/>
       <c r="H49" s="10"/>
     </row>
     <row r="50" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="10"/>
-      <c r="B50" s="69" t="s">
+      <c r="B50" s="114" t="s">
         <v>67</v>
       </c>
-      <c r="C50" s="70"/>
-      <c r="D50" s="71"/>
-      <c r="E50" s="66"/>
-      <c r="F50" s="67"/>
-      <c r="G50" s="68"/>
+      <c r="C50" s="115"/>
+      <c r="D50" s="116"/>
+      <c r="E50" s="111"/>
+      <c r="F50" s="112"/>
+      <c r="G50" s="113"/>
       <c r="H50" s="10"/>
     </row>
     <row r="51" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="10"/>
-      <c r="B51" s="72"/>
-      <c r="C51" s="72"/>
-      <c r="D51" s="72"/>
-      <c r="E51" s="72"/>
-      <c r="F51" s="72"/>
-      <c r="G51" s="72"/>
+      <c r="B51" s="117"/>
+      <c r="C51" s="117"/>
+      <c r="D51" s="117"/>
+      <c r="E51" s="117"/>
+      <c r="F51" s="117"/>
+      <c r="G51" s="117"/>
       <c r="H51" s="10"/>
     </row>
     <row r="52" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
@@ -2730,61 +2809,61 @@
       <c r="B52" s="31" t="s">
         <v>68</v>
       </c>
-      <c r="C52" s="73"/>
-      <c r="D52" s="73"/>
-      <c r="E52" s="73"/>
-      <c r="F52" s="73"/>
-      <c r="G52" s="73"/>
+      <c r="C52" s="118"/>
+      <c r="D52" s="118"/>
+      <c r="E52" s="118"/>
+      <c r="F52" s="118"/>
+      <c r="G52" s="118"/>
       <c r="H52" s="10"/>
     </row>
     <row r="53" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="10"/>
-      <c r="B53" s="74"/>
-      <c r="C53" s="74"/>
-      <c r="D53" s="74"/>
-      <c r="E53" s="74"/>
-      <c r="F53" s="74"/>
-      <c r="G53" s="74"/>
+      <c r="B53" s="119"/>
+      <c r="C53" s="119"/>
+      <c r="D53" s="119"/>
+      <c r="E53" s="119"/>
+      <c r="F53" s="119"/>
+      <c r="G53" s="119"/>
       <c r="H53" s="10"/>
     </row>
     <row r="54" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="10"/>
-      <c r="B54" s="74"/>
-      <c r="C54" s="74"/>
-      <c r="D54" s="74"/>
-      <c r="E54" s="74"/>
-      <c r="F54" s="74"/>
-      <c r="G54" s="74"/>
+      <c r="B54" s="119"/>
+      <c r="C54" s="119"/>
+      <c r="D54" s="119"/>
+      <c r="E54" s="119"/>
+      <c r="F54" s="119"/>
+      <c r="G54" s="119"/>
       <c r="H54" s="10"/>
     </row>
     <row r="55" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="10"/>
-      <c r="B55" s="75"/>
-      <c r="C55" s="75"/>
-      <c r="D55" s="75"/>
-      <c r="E55" s="75"/>
-      <c r="F55" s="75"/>
-      <c r="G55" s="75"/>
+      <c r="B55" s="120"/>
+      <c r="C55" s="120"/>
+      <c r="D55" s="120"/>
+      <c r="E55" s="120"/>
+      <c r="F55" s="120"/>
+      <c r="G55" s="120"/>
       <c r="H55" s="10"/>
     </row>
     <row r="56" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="21"/>
-      <c r="B56" s="46" t="s">
+      <c r="B56" s="103" t="s">
         <v>69</v>
       </c>
-      <c r="C56" s="46"/>
-      <c r="D56" s="46"/>
-      <c r="E56" s="46"/>
-      <c r="F56" s="46"/>
-      <c r="G56" s="46"/>
+      <c r="C56" s="103"/>
+      <c r="D56" s="103"/>
+      <c r="E56" s="103"/>
+      <c r="F56" s="103"/>
+      <c r="G56" s="103"/>
       <c r="H56" s="22"/>
     </row>
     <row r="57" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="22"/>
-      <c r="B57" s="45" t="s">
+      <c r="B57" s="122" t="s">
         <v>70</v>
       </c>
-      <c r="C57" s="45"/>
+      <c r="C57" s="122"/>
       <c r="D57" s="32">
         <v>6</v>
       </c>
@@ -2797,43 +2876,43 @@
     </row>
     <row r="58" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="21"/>
-      <c r="B58" s="46" t="s">
+      <c r="B58" s="103" t="s">
         <v>72</v>
       </c>
-      <c r="C58" s="46"/>
-      <c r="D58" s="46"/>
-      <c r="E58" s="46"/>
-      <c r="F58" s="46"/>
-      <c r="G58" s="46"/>
+      <c r="C58" s="103"/>
+      <c r="D58" s="103"/>
+      <c r="E58" s="103"/>
+      <c r="F58" s="103"/>
+      <c r="G58" s="103"/>
       <c r="H58" s="22"/>
     </row>
     <row r="59" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="22"/>
-      <c r="B59" s="47" t="s">
+      <c r="B59" s="123" t="s">
         <v>73</v>
       </c>
-      <c r="C59" s="47"/>
+      <c r="C59" s="123"/>
       <c r="D59" s="34">
         <f>C61+C62+C64</f>
         <v>0</v>
       </c>
-      <c r="E59" s="48" t="s">
+      <c r="E59" s="124" t="s">
         <v>74</v>
       </c>
-      <c r="F59" s="48"/>
+      <c r="F59" s="124"/>
       <c r="G59" s="20"/>
       <c r="H59" s="22"/>
     </row>
     <row r="60" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="21"/>
-      <c r="B60" s="46" t="s">
+      <c r="B60" s="103" t="s">
         <v>75</v>
       </c>
-      <c r="C60" s="46"/>
-      <c r="D60" s="46"/>
-      <c r="E60" s="46"/>
-      <c r="F60" s="46"/>
-      <c r="G60" s="46"/>
+      <c r="C60" s="103"/>
+      <c r="D60" s="103"/>
+      <c r="E60" s="103"/>
+      <c r="F60" s="103"/>
+      <c r="G60" s="103"/>
       <c r="H60" s="22"/>
     </row>
     <row r="61" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
@@ -2842,14 +2921,14 @@
         <v>90</v>
       </c>
       <c r="C61" s="35"/>
-      <c r="D61" s="49" t="s">
+      <c r="D61" s="125" t="s">
         <v>89</v>
       </c>
-      <c r="E61" s="50"/>
-      <c r="F61" s="50"/>
+      <c r="E61" s="126"/>
+      <c r="F61" s="126"/>
       <c r="G61" s="36">
         <f ca="1">E17</f>
-        <v>45870</v>
+        <v>45973</v>
       </c>
       <c r="H61" s="22"/>
     </row>
@@ -2859,14 +2938,14 @@
         <v>91</v>
       </c>
       <c r="C62" s="37"/>
-      <c r="D62" s="50" t="s">
+      <c r="D62" s="126" t="s">
         <v>76</v>
       </c>
-      <c r="E62" s="50"/>
-      <c r="F62" s="50"/>
+      <c r="E62" s="126"/>
+      <c r="F62" s="126"/>
       <c r="G62" s="36">
         <f ca="1">E17+7</f>
-        <v>45877</v>
+        <v>45980</v>
       </c>
       <c r="H62" s="38" t="s">
         <v>77</v>
@@ -2878,14 +2957,14 @@
         <v>92</v>
       </c>
       <c r="C63" s="37"/>
-      <c r="D63" s="51" t="s">
+      <c r="D63" s="127" t="s">
         <v>78</v>
       </c>
-      <c r="E63" s="51"/>
-      <c r="F63" s="51"/>
+      <c r="E63" s="127"/>
+      <c r="F63" s="127"/>
       <c r="G63" s="36">
         <f ca="1">E17+12</f>
-        <v>45882</v>
+        <v>45985</v>
       </c>
       <c r="H63" s="38" t="s">
         <v>77</v>
@@ -2897,14 +2976,14 @@
         <v>93</v>
       </c>
       <c r="C64" s="37"/>
-      <c r="D64" s="50" t="s">
+      <c r="D64" s="126" t="s">
         <v>79</v>
       </c>
-      <c r="E64" s="50"/>
-      <c r="F64" s="50"/>
+      <c r="E64" s="126"/>
+      <c r="F64" s="126"/>
       <c r="G64" s="36">
         <f ca="1">+G62+26</f>
-        <v>45903</v>
+        <v>46006</v>
       </c>
       <c r="H64" s="38" t="s">
         <v>77</v>
@@ -2912,77 +2991,77 @@
     </row>
     <row r="65" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="10"/>
-      <c r="B65" s="52" t="s">
+      <c r="B65" s="128" t="s">
         <v>80</v>
       </c>
-      <c r="C65" s="52"/>
-      <c r="D65" s="52"/>
-      <c r="E65" s="52"/>
-      <c r="F65" s="52"/>
-      <c r="G65" s="52"/>
+      <c r="C65" s="128"/>
+      <c r="D65" s="128"/>
+      <c r="E65" s="128"/>
+      <c r="F65" s="128"/>
+      <c r="G65" s="128"/>
       <c r="H65" s="39"/>
     </row>
     <row r="66" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="40" t="s">
         <v>81</v>
       </c>
-      <c r="B66" s="53" t="s">
+      <c r="B66" s="129" t="s">
         <v>82</v>
       </c>
-      <c r="C66" s="53"/>
-      <c r="D66" s="53"/>
-      <c r="E66" s="53"/>
-      <c r="F66" s="53"/>
-      <c r="G66" s="53"/>
+      <c r="C66" s="129"/>
+      <c r="D66" s="129"/>
+      <c r="E66" s="129"/>
+      <c r="F66" s="129"/>
+      <c r="G66" s="129"/>
     </row>
     <row r="67" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B67" s="44" t="s">
+      <c r="B67" s="121" t="s">
         <v>94</v>
       </c>
-      <c r="C67" s="44"/>
-      <c r="D67" s="44"/>
-      <c r="E67" s="44"/>
-      <c r="F67" s="44" t="s">
+      <c r="C67" s="121"/>
+      <c r="D67" s="121"/>
+      <c r="E67" s="121"/>
+      <c r="F67" s="121" t="s">
         <v>83</v>
       </c>
-      <c r="G67" s="44"/>
-      <c r="H67" s="44"/>
+      <c r="G67" s="121"/>
+      <c r="H67" s="121"/>
     </row>
     <row r="68" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B68" s="43" t="s">
+      <c r="B68" s="130" t="s">
         <v>84</v>
       </c>
-      <c r="C68" s="43"/>
-      <c r="D68" s="43"/>
-      <c r="E68" s="43"/>
-      <c r="F68" s="44" t="s">
+      <c r="C68" s="130"/>
+      <c r="D68" s="130"/>
+      <c r="E68" s="130"/>
+      <c r="F68" s="121" t="s">
         <v>85</v>
       </c>
-      <c r="G68" s="44"/>
-      <c r="H68" s="44"/>
+      <c r="G68" s="121"/>
+      <c r="H68" s="121"/>
     </row>
     <row r="69" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B69" s="43" t="s">
+      <c r="B69" s="130" t="s">
         <v>86</v>
       </c>
-      <c r="C69" s="43"/>
-      <c r="D69" s="43"/>
-      <c r="E69" s="43"/>
-      <c r="F69" s="44" t="s">
+      <c r="C69" s="130"/>
+      <c r="D69" s="130"/>
+      <c r="E69" s="130"/>
+      <c r="F69" s="121" t="s">
         <v>87</v>
       </c>
-      <c r="G69" s="44"/>
-      <c r="H69" s="44"/>
+      <c r="G69" s="121"/>
+      <c r="H69" s="121"/>
     </row>
     <row r="70" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B70" s="44" t="s">
+      <c r="B70" s="121" t="s">
         <v>88</v>
       </c>
-      <c r="C70" s="44"/>
-      <c r="D70" s="44"/>
-      <c r="E70" s="44"/>
-      <c r="F70" s="44"/>
-      <c r="G70" s="44"/>
+      <c r="C70" s="121"/>
+      <c r="D70" s="121"/>
+      <c r="E70" s="121"/>
+      <c r="F70" s="121"/>
+      <c r="G70" s="121"/>
     </row>
     <row r="71" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B71" s="41"/>
@@ -3010,37 +3089,51 @@
     <protectedRange algorithmName="SHA-512" hashValue="1IwEtpPovyRjspz9ti3J5udl070IPZ9gDlGmM3ZH/lFyQlLVVL2qbaMds7kHvZZkPq7VvowLV2MqpNnf8owpjQ==" saltValue="SwYyjj//I75seGLqQP0hyQ==" spinCount="100000" sqref="E37:G38 E39" name="Rango2_2"/>
   </protectedRanges>
   <mergeCells count="91">
-    <mergeCell ref="B9:G10"/>
-    <mergeCell ref="D4:F4"/>
-    <mergeCell ref="D5:F5"/>
-    <mergeCell ref="D6:F6"/>
-    <mergeCell ref="D7:F7"/>
-    <mergeCell ref="A8:H8"/>
-    <mergeCell ref="B21:D21"/>
-    <mergeCell ref="E21:G21"/>
-    <mergeCell ref="B11:E11"/>
-    <mergeCell ref="B12:G12"/>
-    <mergeCell ref="B13:G13"/>
-    <mergeCell ref="B15:E15"/>
-    <mergeCell ref="B16:E16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B18:G18"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="E19:G19"/>
-    <mergeCell ref="B20:D20"/>
-    <mergeCell ref="E20:G20"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="E22:G22"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="E23:G23"/>
-    <mergeCell ref="B24:D24"/>
-    <mergeCell ref="E24:G24"/>
-    <mergeCell ref="B25:D25"/>
-    <mergeCell ref="E25:G25"/>
-    <mergeCell ref="B26:D26"/>
-    <mergeCell ref="E26:G26"/>
-    <mergeCell ref="B27:D27"/>
-    <mergeCell ref="E27:G27"/>
+    <mergeCell ref="B68:E68"/>
+    <mergeCell ref="F68:H68"/>
+    <mergeCell ref="B69:E69"/>
+    <mergeCell ref="F69:H69"/>
+    <mergeCell ref="B70:E70"/>
+    <mergeCell ref="F70:G70"/>
+    <mergeCell ref="B67:E67"/>
+    <mergeCell ref="F67:H67"/>
+    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="B58:G58"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="E59:F59"/>
+    <mergeCell ref="B60:G60"/>
+    <mergeCell ref="D61:F61"/>
+    <mergeCell ref="D62:F62"/>
+    <mergeCell ref="D63:F63"/>
+    <mergeCell ref="D64:F64"/>
+    <mergeCell ref="B65:G65"/>
+    <mergeCell ref="B66:G66"/>
+    <mergeCell ref="B56:G56"/>
+    <mergeCell ref="B43:D43"/>
+    <mergeCell ref="B44:G44"/>
+    <mergeCell ref="B45:D47"/>
+    <mergeCell ref="E45:G46"/>
+    <mergeCell ref="E47:G48"/>
+    <mergeCell ref="B48:D49"/>
+    <mergeCell ref="E49:G50"/>
+    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="B51:G51"/>
+    <mergeCell ref="C52:G52"/>
+    <mergeCell ref="B53:G53"/>
+    <mergeCell ref="B54:G54"/>
+    <mergeCell ref="B55:G55"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="E40:G40"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="E41:G41"/>
+    <mergeCell ref="B42:D42"/>
+    <mergeCell ref="E42:G42"/>
+    <mergeCell ref="B37:D37"/>
+    <mergeCell ref="E37:G37"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="E38:G38"/>
+    <mergeCell ref="B39:D39"/>
+    <mergeCell ref="E39:G39"/>
     <mergeCell ref="B35:D36"/>
     <mergeCell ref="E35:G35"/>
     <mergeCell ref="E36:G36"/>
@@ -3056,58 +3149,44 @@
     <mergeCell ref="E33:G33"/>
     <mergeCell ref="B34:D34"/>
     <mergeCell ref="E34:G34"/>
-    <mergeCell ref="B37:D37"/>
-    <mergeCell ref="E37:G37"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="E38:G38"/>
-    <mergeCell ref="B39:D39"/>
-    <mergeCell ref="E39:G39"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="E40:G40"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="E41:G41"/>
-    <mergeCell ref="B42:D42"/>
-    <mergeCell ref="E42:G42"/>
-    <mergeCell ref="B56:G56"/>
-    <mergeCell ref="B43:D43"/>
-    <mergeCell ref="B44:G44"/>
-    <mergeCell ref="B45:D47"/>
-    <mergeCell ref="E45:G46"/>
-    <mergeCell ref="E47:G48"/>
-    <mergeCell ref="B48:D49"/>
-    <mergeCell ref="E49:G50"/>
-    <mergeCell ref="B50:D50"/>
-    <mergeCell ref="B51:G51"/>
-    <mergeCell ref="C52:G52"/>
-    <mergeCell ref="B53:G53"/>
-    <mergeCell ref="B54:G54"/>
-    <mergeCell ref="B55:G55"/>
-    <mergeCell ref="B67:E67"/>
-    <mergeCell ref="F67:H67"/>
-    <mergeCell ref="B57:C57"/>
-    <mergeCell ref="B58:G58"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="E59:F59"/>
-    <mergeCell ref="B60:G60"/>
-    <mergeCell ref="D61:F61"/>
-    <mergeCell ref="D62:F62"/>
-    <mergeCell ref="D63:F63"/>
-    <mergeCell ref="D64:F64"/>
-    <mergeCell ref="B65:G65"/>
-    <mergeCell ref="B66:G66"/>
-    <mergeCell ref="B68:E68"/>
-    <mergeCell ref="F68:H68"/>
-    <mergeCell ref="B69:E69"/>
-    <mergeCell ref="F69:H69"/>
-    <mergeCell ref="B70:E70"/>
-    <mergeCell ref="F70:G70"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="E25:G25"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="E26:G26"/>
+    <mergeCell ref="B27:D27"/>
+    <mergeCell ref="E27:G27"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="E22:G22"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="E23:G23"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="E24:G24"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="E21:G21"/>
+    <mergeCell ref="B11:E11"/>
+    <mergeCell ref="B12:G12"/>
+    <mergeCell ref="B13:G13"/>
+    <mergeCell ref="B15:E15"/>
+    <mergeCell ref="B16:E16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B18:G18"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="E19:G19"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="E20:G20"/>
+    <mergeCell ref="B9:G10"/>
+    <mergeCell ref="D4:F4"/>
+    <mergeCell ref="D5:F5"/>
+    <mergeCell ref="D6:F6"/>
+    <mergeCell ref="D7:F7"/>
+    <mergeCell ref="A8:H8"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="D7" r:id="rId1" display="https://www.planosperu.com.pe" xr:uid="{506D083F-F460-4953-991A-891366CADB27}"/>
   </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.59055118110236227" right="0.59055118110236227" top="0.59055118110236227" bottom="0" header="0" footer="0"/>
-  <pageSetup paperSize="9" scale="89" orientation="portrait" r:id="rId2"/>
+  <pageSetup paperSize="9" scale="90" orientation="portrait" r:id="rId2"/>
   <drawing r:id="rId3"/>
 </worksheet>
 </file>
--- a/backend/docs/TRA-DEC.xlsx
+++ b/backend/docs/TRA-DEC.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell Latitude\Documents\Projects\planos-react-app\backend\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\planos-react-app\backend\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E403C796-0EE6-44A9-8CC3-FEAC49C97C67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B94EDC6-6286-429F-BF15-CD20D4985245}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{03CDC904-23BA-49AE-AA6F-5DD301F77889}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{03CDC904-23BA-49AE-AA6F-5DD301F77889}"/>
   </bookViews>
   <sheets>
     <sheet name="TRA-DEC" sheetId="2" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="99">
   <si>
     <t xml:space="preserve">                                                                                                                  </t>
   </si>
@@ -303,9 +303,6 @@
   </si>
   <si>
     <t xml:space="preserve">Arq. Rodolfo Wilber Mogrovejo Huamani CAP N° 24431 </t>
-  </si>
-  <si>
-    <t>Ing. Sanitario José Francisco Javier Zela Steban CIP: 130333</t>
   </si>
   <si>
     <t>A la Aprobación de la Presente Proforma y Medición del Inmueble</t>
@@ -806,20 +803,248 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection hidden="1"/>
@@ -829,6 +1054,26 @@
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection hidden="1"/>
     </xf>
@@ -860,18 +1105,6 @@
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection hidden="1"/>
@@ -880,256 +1113,20 @@
       <alignment horizontal="left" vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -2196,86 +2193,86 @@
       <c r="C4" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="44" t="s">
-        <v>98</v>
-      </c>
-      <c r="E4" s="44"/>
-      <c r="F4" s="44"/>
+      <c r="D4" s="126" t="s">
+        <v>97</v>
+      </c>
+      <c r="E4" s="126"/>
+      <c r="F4" s="126"/>
       <c r="G4" s="2"/>
     </row>
     <row r="5" spans="1:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C5" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="45" t="s">
-        <v>99</v>
-      </c>
-      <c r="E5" s="45"/>
-      <c r="F5" s="45"/>
+      <c r="D5" s="127" t="s">
+        <v>98</v>
+      </c>
+      <c r="E5" s="127"/>
+      <c r="F5" s="127"/>
       <c r="G5" s="3"/>
     </row>
     <row r="6" spans="1:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C6" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="D6" s="46" t="s">
-        <v>97</v>
-      </c>
-      <c r="E6" s="46"/>
-      <c r="F6" s="46"/>
+      <c r="D6" s="128" t="s">
+        <v>96</v>
+      </c>
+      <c r="E6" s="128"/>
+      <c r="F6" s="128"/>
       <c r="G6" s="4"/>
     </row>
     <row r="7" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C7" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="D7" s="47" t="s">
-        <v>96</v>
-      </c>
-      <c r="E7" s="47"/>
-      <c r="F7" s="47"/>
+      <c r="D7" s="129" t="s">
+        <v>95</v>
+      </c>
+      <c r="E7" s="129"/>
+      <c r="F7" s="129"/>
       <c r="G7" s="4"/>
     </row>
     <row r="8" spans="1:8" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="48"/>
-      <c r="B8" s="48"/>
-      <c r="C8" s="48"/>
-      <c r="D8" s="48"/>
-      <c r="E8" s="48"/>
-      <c r="F8" s="48"/>
-      <c r="G8" s="48"/>
-      <c r="H8" s="48"/>
+      <c r="A8" s="130"/>
+      <c r="B8" s="130"/>
+      <c r="C8" s="130"/>
+      <c r="D8" s="130"/>
+      <c r="E8" s="130"/>
+      <c r="F8" s="130"/>
+      <c r="G8" s="130"/>
+      <c r="H8" s="130"/>
     </row>
     <row r="9" spans="1:8" s="5" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="43" t="s">
+      <c r="B9" s="125" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="43"/>
-      <c r="D9" s="43"/>
-      <c r="E9" s="43"/>
-      <c r="F9" s="43"/>
-      <c r="G9" s="43"/>
+      <c r="C9" s="125"/>
+      <c r="D9" s="125"/>
+      <c r="E9" s="125"/>
+      <c r="F9" s="125"/>
+      <c r="G9" s="125"/>
       <c r="H9" s="6"/>
     </row>
     <row r="10" spans="1:8" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="43"/>
-      <c r="C10" s="43"/>
-      <c r="D10" s="43"/>
-      <c r="E10" s="43"/>
-      <c r="F10" s="43"/>
-      <c r="G10" s="43"/>
+      <c r="B10" s="125"/>
+      <c r="C10" s="125"/>
+      <c r="D10" s="125"/>
+      <c r="E10" s="125"/>
+      <c r="F10" s="125"/>
+      <c r="G10" s="125"/>
       <c r="H10" s="6"/>
     </row>
     <row r="11" spans="1:8" s="11" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B11" s="52" t="s">
+      <c r="B11" s="116" t="s">
         <v>7</v>
       </c>
-      <c r="C11" s="52"/>
-      <c r="D11" s="52"/>
-      <c r="E11" s="52"/>
+      <c r="C11" s="116"/>
+      <c r="D11" s="116"/>
+      <c r="E11" s="116"/>
       <c r="F11" s="8" t="s">
         <v>8</v>
       </c>
@@ -2284,27 +2281,27 @@
     </row>
     <row r="12" spans="1:8" s="11" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="7"/>
-      <c r="B12" s="52"/>
-      <c r="C12" s="52"/>
-      <c r="D12" s="52"/>
-      <c r="E12" s="52"/>
-      <c r="F12" s="52"/>
-      <c r="G12" s="52"/>
+      <c r="B12" s="116"/>
+      <c r="C12" s="116"/>
+      <c r="D12" s="116"/>
+      <c r="E12" s="116"/>
+      <c r="F12" s="116"/>
+      <c r="G12" s="116"/>
       <c r="H12" s="10"/>
     </row>
     <row r="13" spans="1:8" s="11" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="12"/>
-      <c r="B13" s="52"/>
-      <c r="C13" s="52"/>
-      <c r="D13" s="52"/>
-      <c r="E13" s="52"/>
-      <c r="F13" s="52"/>
-      <c r="G13" s="52"/>
+      <c r="B13" s="116"/>
+      <c r="C13" s="116"/>
+      <c r="D13" s="116"/>
+      <c r="E13" s="116"/>
+      <c r="F13" s="116"/>
+      <c r="G13" s="116"/>
       <c r="H13" s="10"/>
     </row>
     <row r="14" spans="1:8" s="11" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B14" s="42"/>
       <c r="C14" s="13" t="s">
@@ -2324,10 +2321,10 @@
       <c r="A15" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="B15" s="52"/>
-      <c r="C15" s="52"/>
-      <c r="D15" s="52"/>
-      <c r="E15" s="52"/>
+      <c r="B15" s="116"/>
+      <c r="C15" s="116"/>
+      <c r="D15" s="116"/>
+      <c r="E15" s="116"/>
       <c r="F15" s="13" t="s">
         <v>13</v>
       </c>
@@ -2336,10 +2333,10 @@
     </row>
     <row r="16" spans="1:8" s="11" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="12"/>
-      <c r="B16" s="53"/>
-      <c r="C16" s="53"/>
-      <c r="D16" s="53"/>
-      <c r="E16" s="53"/>
+      <c r="B16" s="117"/>
+      <c r="C16" s="117"/>
+      <c r="D16" s="117"/>
+      <c r="E16" s="117"/>
       <c r="F16" s="13" t="s">
         <v>14</v>
       </c>
@@ -2350,14 +2347,14 @@
       <c r="A17" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="B17" s="52"/>
-      <c r="C17" s="52"/>
+      <c r="B17" s="116"/>
+      <c r="C17" s="116"/>
       <c r="D17" s="18" t="s">
         <v>16</v>
       </c>
       <c r="E17" s="19">
         <f ca="1">TODAY()</f>
-        <v>45973</v>
+        <v>46163</v>
       </c>
       <c r="F17" s="15"/>
       <c r="G17" s="15"/>
@@ -2365,443 +2362,443 @@
     </row>
     <row r="18" spans="1:8" s="11" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="20"/>
-      <c r="B18" s="54"/>
-      <c r="C18" s="54"/>
-      <c r="D18" s="54"/>
-      <c r="E18" s="54"/>
-      <c r="F18" s="54"/>
-      <c r="G18" s="54"/>
+      <c r="B18" s="118"/>
+      <c r="C18" s="118"/>
+      <c r="D18" s="118"/>
+      <c r="E18" s="118"/>
+      <c r="F18" s="118"/>
+      <c r="G18" s="118"/>
       <c r="H18" s="20"/>
     </row>
     <row r="19" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="21"/>
-      <c r="B19" s="55" t="s">
+      <c r="B19" s="119" t="s">
         <v>17</v>
       </c>
-      <c r="C19" s="56"/>
-      <c r="D19" s="57"/>
-      <c r="E19" s="58"/>
-      <c r="F19" s="58"/>
-      <c r="G19" s="58"/>
+      <c r="C19" s="120"/>
+      <c r="D19" s="121"/>
+      <c r="E19" s="122"/>
+      <c r="F19" s="122"/>
+      <c r="G19" s="122"/>
       <c r="H19" s="22"/>
     </row>
     <row r="20" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="10"/>
-      <c r="B20" s="59" t="s">
+      <c r="B20" s="85" t="s">
         <v>18</v>
       </c>
-      <c r="C20" s="60"/>
-      <c r="D20" s="61"/>
-      <c r="E20" s="62" t="s">
+      <c r="C20" s="86"/>
+      <c r="D20" s="87"/>
+      <c r="E20" s="123" t="s">
         <v>19</v>
       </c>
-      <c r="F20" s="62"/>
-      <c r="G20" s="63"/>
+      <c r="F20" s="123"/>
+      <c r="G20" s="124"/>
       <c r="H20" s="10"/>
     </row>
     <row r="21" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="10"/>
-      <c r="B21" s="49" t="s">
+      <c r="B21" s="108" t="s">
         <v>20</v>
       </c>
-      <c r="C21" s="50"/>
-      <c r="D21" s="51"/>
-      <c r="E21" s="50" t="s">
+      <c r="C21" s="109"/>
+      <c r="D21" s="110"/>
+      <c r="E21" s="109" t="s">
         <v>21</v>
       </c>
-      <c r="F21" s="50"/>
-      <c r="G21" s="51"/>
+      <c r="F21" s="109"/>
+      <c r="G21" s="110"/>
       <c r="H21" s="10"/>
     </row>
     <row r="22" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="10"/>
-      <c r="B22" s="64" t="s">
+      <c r="B22" s="57" t="s">
         <v>22</v>
       </c>
-      <c r="C22" s="65"/>
-      <c r="D22" s="65"/>
-      <c r="E22" s="66"/>
-      <c r="F22" s="66"/>
-      <c r="G22" s="67"/>
+      <c r="C22" s="58"/>
+      <c r="D22" s="58"/>
+      <c r="E22" s="114"/>
+      <c r="F22" s="114"/>
+      <c r="G22" s="115"/>
       <c r="H22" s="10"/>
     </row>
     <row r="23" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="10"/>
-      <c r="B23" s="49" t="s">
+      <c r="B23" s="108" t="s">
         <v>23</v>
       </c>
-      <c r="C23" s="50"/>
-      <c r="D23" s="51"/>
-      <c r="E23" s="49" t="s">
+      <c r="C23" s="109"/>
+      <c r="D23" s="110"/>
+      <c r="E23" s="108" t="s">
         <v>24</v>
       </c>
-      <c r="F23" s="50"/>
-      <c r="G23" s="51"/>
+      <c r="F23" s="109"/>
+      <c r="G23" s="110"/>
       <c r="H23" s="10"/>
     </row>
     <row r="24" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="10"/>
-      <c r="B24" s="59" t="s">
+      <c r="B24" s="85" t="s">
         <v>25</v>
       </c>
-      <c r="C24" s="60"/>
-      <c r="D24" s="61"/>
-      <c r="E24" s="49" t="s">
+      <c r="C24" s="86"/>
+      <c r="D24" s="87"/>
+      <c r="E24" s="108" t="s">
         <v>26</v>
       </c>
-      <c r="F24" s="50"/>
-      <c r="G24" s="51"/>
+      <c r="F24" s="109"/>
+      <c r="G24" s="110"/>
       <c r="H24" s="10"/>
     </row>
     <row r="25" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="24"/>
-      <c r="B25" s="49" t="s">
+      <c r="B25" s="108" t="s">
         <v>27</v>
       </c>
-      <c r="C25" s="50"/>
-      <c r="D25" s="51"/>
-      <c r="E25" s="59" t="s">
+      <c r="C25" s="109"/>
+      <c r="D25" s="110"/>
+      <c r="E25" s="85" t="s">
         <v>28</v>
       </c>
-      <c r="F25" s="60"/>
-      <c r="G25" s="61"/>
+      <c r="F25" s="86"/>
+      <c r="G25" s="87"/>
       <c r="H25" s="10"/>
     </row>
     <row r="26" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="25"/>
-      <c r="B26" s="49" t="s">
+      <c r="B26" s="108" t="s">
         <v>29</v>
       </c>
-      <c r="C26" s="50"/>
-      <c r="D26" s="51"/>
-      <c r="E26" s="49" t="s">
+      <c r="C26" s="109"/>
+      <c r="D26" s="110"/>
+      <c r="E26" s="108" t="s">
         <v>30</v>
       </c>
-      <c r="F26" s="50"/>
-      <c r="G26" s="51"/>
+      <c r="F26" s="109"/>
+      <c r="G26" s="110"/>
       <c r="H26" s="10"/>
     </row>
     <row r="27" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="25"/>
-      <c r="B27" s="68" t="s">
+      <c r="B27" s="111" t="s">
         <v>31</v>
       </c>
-      <c r="C27" s="69"/>
-      <c r="D27" s="70"/>
-      <c r="E27" s="49" t="s">
+      <c r="C27" s="112"/>
+      <c r="D27" s="113"/>
+      <c r="E27" s="108" t="s">
         <v>32</v>
       </c>
-      <c r="F27" s="50"/>
-      <c r="G27" s="51"/>
+      <c r="F27" s="109"/>
+      <c r="G27" s="110"/>
       <c r="H27" s="10"/>
     </row>
     <row r="28" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="25"/>
-      <c r="B28" s="77" t="s">
+      <c r="B28" s="94" t="s">
         <v>33</v>
       </c>
-      <c r="C28" s="78"/>
-      <c r="D28" s="79"/>
-      <c r="E28" s="80" t="s">
+      <c r="C28" s="95"/>
+      <c r="D28" s="96"/>
+      <c r="E28" s="97" t="s">
         <v>34</v>
       </c>
-      <c r="F28" s="81"/>
-      <c r="G28" s="82"/>
+      <c r="F28" s="98"/>
+      <c r="G28" s="99"/>
       <c r="H28" s="10"/>
     </row>
     <row r="29" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="25"/>
-      <c r="B29" s="64" t="s">
+      <c r="B29" s="57" t="s">
         <v>35</v>
       </c>
-      <c r="C29" s="65"/>
-      <c r="D29" s="65"/>
-      <c r="E29" s="83"/>
-      <c r="F29" s="83"/>
-      <c r="G29" s="84"/>
+      <c r="C29" s="58"/>
+      <c r="D29" s="58"/>
+      <c r="E29" s="100"/>
+      <c r="F29" s="100"/>
+      <c r="G29" s="101"/>
       <c r="H29" s="10"/>
     </row>
     <row r="30" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="26"/>
-      <c r="B30" s="85" t="s">
+      <c r="B30" s="102" t="s">
         <v>36</v>
       </c>
-      <c r="C30" s="86"/>
-      <c r="D30" s="87"/>
-      <c r="E30" s="85" t="s">
+      <c r="C30" s="103"/>
+      <c r="D30" s="104"/>
+      <c r="E30" s="102" t="s">
         <v>37</v>
       </c>
-      <c r="F30" s="86"/>
-      <c r="G30" s="87"/>
+      <c r="F30" s="103"/>
+      <c r="G30" s="104"/>
       <c r="H30" s="10"/>
     </row>
     <row r="31" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="26"/>
-      <c r="B31" s="74" t="s">
+      <c r="B31" s="54" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="75"/>
-      <c r="D31" s="76"/>
-      <c r="E31" s="74" t="s">
+      <c r="C31" s="55"/>
+      <c r="D31" s="56"/>
+      <c r="E31" s="54" t="s">
         <v>39</v>
       </c>
-      <c r="F31" s="75"/>
-      <c r="G31" s="76"/>
+      <c r="F31" s="55"/>
+      <c r="G31" s="56"/>
       <c r="H31" s="10"/>
     </row>
     <row r="32" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="27"/>
-      <c r="B32" s="88" t="s">
+      <c r="B32" s="105" t="s">
         <v>40</v>
       </c>
-      <c r="C32" s="89"/>
-      <c r="D32" s="90"/>
-      <c r="E32" s="74" t="s">
+      <c r="C32" s="106"/>
+      <c r="D32" s="107"/>
+      <c r="E32" s="54" t="s">
         <v>41</v>
       </c>
-      <c r="F32" s="75"/>
-      <c r="G32" s="76"/>
+      <c r="F32" s="55"/>
+      <c r="G32" s="56"/>
       <c r="H32" s="10"/>
     </row>
     <row r="33" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="10"/>
-      <c r="B33" s="88"/>
-      <c r="C33" s="89"/>
-      <c r="D33" s="90"/>
-      <c r="E33" s="74" t="s">
+      <c r="B33" s="105"/>
+      <c r="C33" s="106"/>
+      <c r="D33" s="107"/>
+      <c r="E33" s="54" t="s">
         <v>42</v>
       </c>
-      <c r="F33" s="75"/>
-      <c r="G33" s="76"/>
+      <c r="F33" s="55"/>
+      <c r="G33" s="56"/>
       <c r="H33" s="10"/>
     </row>
     <row r="34" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="10"/>
-      <c r="B34" s="74" t="s">
+      <c r="B34" s="54" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="75"/>
-      <c r="D34" s="76"/>
-      <c r="E34" s="74" t="s">
+      <c r="C34" s="55"/>
+      <c r="D34" s="56"/>
+      <c r="E34" s="54" t="s">
         <v>44</v>
       </c>
-      <c r="F34" s="75"/>
-      <c r="G34" s="76"/>
+      <c r="F34" s="55"/>
+      <c r="G34" s="56"/>
       <c r="H34" s="10"/>
     </row>
     <row r="35" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="10"/>
-      <c r="B35" s="71" t="s">
+      <c r="B35" s="91" t="s">
         <v>45</v>
       </c>
-      <c r="C35" s="72"/>
-      <c r="D35" s="73"/>
-      <c r="E35" s="74" t="s">
+      <c r="C35" s="92"/>
+      <c r="D35" s="93"/>
+      <c r="E35" s="54" t="s">
         <v>46</v>
       </c>
-      <c r="F35" s="75"/>
-      <c r="G35" s="76"/>
+      <c r="F35" s="55"/>
+      <c r="G35" s="56"/>
       <c r="H35" s="10"/>
     </row>
     <row r="36" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="10"/>
-      <c r="B36" s="71"/>
-      <c r="C36" s="72"/>
-      <c r="D36" s="73"/>
-      <c r="E36" s="74" t="s">
+      <c r="B36" s="91"/>
+      <c r="C36" s="92"/>
+      <c r="D36" s="93"/>
+      <c r="E36" s="54" t="s">
         <v>47</v>
       </c>
-      <c r="F36" s="75"/>
-      <c r="G36" s="76"/>
+      <c r="F36" s="55"/>
+      <c r="G36" s="56"/>
       <c r="H36" s="10"/>
     </row>
     <row r="37" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="10"/>
-      <c r="B37" s="59" t="s">
+      <c r="B37" s="85" t="s">
         <v>48</v>
       </c>
-      <c r="C37" s="60"/>
-      <c r="D37" s="61"/>
-      <c r="E37" s="91" t="s">
+      <c r="C37" s="86"/>
+      <c r="D37" s="87"/>
+      <c r="E37" s="79" t="s">
         <v>49</v>
       </c>
-      <c r="F37" s="92"/>
-      <c r="G37" s="93"/>
+      <c r="F37" s="80"/>
+      <c r="G37" s="81"/>
       <c r="H37" s="10"/>
     </row>
     <row r="38" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="10"/>
-      <c r="B38" s="74" t="s">
+      <c r="B38" s="54" t="s">
         <v>50</v>
       </c>
-      <c r="C38" s="75"/>
-      <c r="D38" s="76"/>
-      <c r="E38" s="91" t="s">
+      <c r="C38" s="55"/>
+      <c r="D38" s="56"/>
+      <c r="E38" s="79" t="s">
         <v>51</v>
       </c>
-      <c r="F38" s="92"/>
-      <c r="G38" s="93"/>
+      <c r="F38" s="80"/>
+      <c r="G38" s="81"/>
       <c r="H38" s="10"/>
     </row>
     <row r="39" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="10"/>
-      <c r="B39" s="74" t="s">
+      <c r="B39" s="54" t="s">
         <v>52</v>
       </c>
-      <c r="C39" s="75"/>
-      <c r="D39" s="76"/>
-      <c r="E39" s="94" t="s">
+      <c r="C39" s="55"/>
+      <c r="D39" s="56"/>
+      <c r="E39" s="88" t="s">
         <v>53</v>
       </c>
-      <c r="F39" s="95"/>
-      <c r="G39" s="96"/>
+      <c r="F39" s="89"/>
+      <c r="G39" s="90"/>
       <c r="H39" s="10"/>
     </row>
     <row r="40" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="10"/>
-      <c r="B40" s="74" t="s">
+      <c r="B40" s="54" t="s">
         <v>54</v>
       </c>
-      <c r="C40" s="75"/>
-      <c r="D40" s="76"/>
-      <c r="E40" s="97" t="s">
+      <c r="C40" s="55"/>
+      <c r="D40" s="56"/>
+      <c r="E40" s="76" t="s">
         <v>55</v>
       </c>
-      <c r="F40" s="98"/>
-      <c r="G40" s="99"/>
+      <c r="F40" s="77"/>
+      <c r="G40" s="78"/>
       <c r="H40" s="10"/>
     </row>
     <row r="41" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="10"/>
-      <c r="B41" s="74" t="s">
+      <c r="B41" s="54" t="s">
         <v>56</v>
       </c>
-      <c r="C41" s="75"/>
-      <c r="D41" s="76"/>
-      <c r="E41" s="91" t="s">
+      <c r="C41" s="55"/>
+      <c r="D41" s="56"/>
+      <c r="E41" s="79" t="s">
         <v>57</v>
       </c>
-      <c r="F41" s="92"/>
-      <c r="G41" s="93"/>
+      <c r="F41" s="80"/>
+      <c r="G41" s="81"/>
       <c r="H41" s="10"/>
     </row>
     <row r="42" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="10"/>
-      <c r="B42" s="74" t="s">
+      <c r="B42" s="54" t="s">
         <v>58</v>
       </c>
-      <c r="C42" s="75"/>
-      <c r="D42" s="76"/>
-      <c r="E42" s="100" t="s">
+      <c r="C42" s="55"/>
+      <c r="D42" s="56"/>
+      <c r="E42" s="82" t="s">
         <v>59</v>
       </c>
-      <c r="F42" s="101"/>
-      <c r="G42" s="102"/>
+      <c r="F42" s="83"/>
+      <c r="G42" s="84"/>
       <c r="H42" s="10"/>
     </row>
     <row r="43" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="10"/>
-      <c r="B43" s="74" t="s">
+      <c r="B43" s="54" t="s">
         <v>60</v>
       </c>
-      <c r="C43" s="75"/>
-      <c r="D43" s="76"/>
+      <c r="C43" s="55"/>
+      <c r="D43" s="56"/>
       <c r="E43" s="28"/>
       <c r="F43" s="29"/>
       <c r="G43" s="30"/>
       <c r="H43" s="10"/>
     </row>
     <row r="44" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B44" s="64" t="s">
+      <c r="B44" s="57" t="s">
         <v>61</v>
       </c>
-      <c r="C44" s="65"/>
-      <c r="D44" s="65"/>
-      <c r="E44" s="65"/>
-      <c r="F44" s="65"/>
-      <c r="G44" s="104"/>
+      <c r="C44" s="58"/>
+      <c r="D44" s="58"/>
+      <c r="E44" s="58"/>
+      <c r="F44" s="58"/>
+      <c r="G44" s="59"/>
       <c r="H44" s="10"/>
     </row>
     <row r="45" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="10"/>
-      <c r="B45" s="105" t="s">
+      <c r="B45" s="60" t="s">
         <v>62</v>
       </c>
-      <c r="C45" s="106"/>
-      <c r="D45" s="107"/>
-      <c r="E45" s="105" t="s">
+      <c r="C45" s="61"/>
+      <c r="D45" s="62"/>
+      <c r="E45" s="60" t="s">
         <v>63</v>
       </c>
-      <c r="F45" s="106"/>
-      <c r="G45" s="107"/>
+      <c r="F45" s="61"/>
+      <c r="G45" s="62"/>
       <c r="H45" s="10"/>
     </row>
     <row r="46" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="10"/>
-      <c r="B46" s="108"/>
-      <c r="C46" s="109"/>
-      <c r="D46" s="110"/>
-      <c r="E46" s="108"/>
-      <c r="F46" s="109"/>
-      <c r="G46" s="110"/>
+      <c r="B46" s="63"/>
+      <c r="C46" s="64"/>
+      <c r="D46" s="65"/>
+      <c r="E46" s="63"/>
+      <c r="F46" s="64"/>
+      <c r="G46" s="65"/>
       <c r="H46" s="10"/>
     </row>
     <row r="47" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="10"/>
-      <c r="B47" s="108"/>
-      <c r="C47" s="109"/>
-      <c r="D47" s="110"/>
-      <c r="E47" s="108" t="s">
+      <c r="B47" s="63"/>
+      <c r="C47" s="64"/>
+      <c r="D47" s="65"/>
+      <c r="E47" s="63" t="s">
         <v>64</v>
       </c>
-      <c r="F47" s="109"/>
-      <c r="G47" s="110"/>
+      <c r="F47" s="64"/>
+      <c r="G47" s="65"/>
       <c r="H47" s="10"/>
     </row>
     <row r="48" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="10"/>
-      <c r="B48" s="108" t="s">
+      <c r="B48" s="63" t="s">
         <v>65</v>
       </c>
-      <c r="C48" s="109"/>
-      <c r="D48" s="110"/>
-      <c r="E48" s="108"/>
-      <c r="F48" s="109"/>
-      <c r="G48" s="110"/>
+      <c r="C48" s="64"/>
+      <c r="D48" s="65"/>
+      <c r="E48" s="63"/>
+      <c r="F48" s="64"/>
+      <c r="G48" s="65"/>
       <c r="H48" s="10"/>
     </row>
     <row r="49" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="10"/>
-      <c r="B49" s="108"/>
-      <c r="C49" s="109"/>
-      <c r="D49" s="110"/>
-      <c r="E49" s="108" t="s">
+      <c r="B49" s="63"/>
+      <c r="C49" s="64"/>
+      <c r="D49" s="65"/>
+      <c r="E49" s="63" t="s">
         <v>66</v>
       </c>
-      <c r="F49" s="109"/>
-      <c r="G49" s="110"/>
+      <c r="F49" s="64"/>
+      <c r="G49" s="65"/>
       <c r="H49" s="10"/>
     </row>
     <row r="50" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="10"/>
-      <c r="B50" s="114" t="s">
+      <c r="B50" s="69" t="s">
         <v>67</v>
       </c>
-      <c r="C50" s="115"/>
-      <c r="D50" s="116"/>
-      <c r="E50" s="111"/>
-      <c r="F50" s="112"/>
-      <c r="G50" s="113"/>
+      <c r="C50" s="70"/>
+      <c r="D50" s="71"/>
+      <c r="E50" s="66"/>
+      <c r="F50" s="67"/>
+      <c r="G50" s="68"/>
       <c r="H50" s="10"/>
     </row>
     <row r="51" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="10"/>
-      <c r="B51" s="117"/>
-      <c r="C51" s="117"/>
-      <c r="D51" s="117"/>
-      <c r="E51" s="117"/>
-      <c r="F51" s="117"/>
-      <c r="G51" s="117"/>
+      <c r="B51" s="72"/>
+      <c r="C51" s="72"/>
+      <c r="D51" s="72"/>
+      <c r="E51" s="72"/>
+      <c r="F51" s="72"/>
+      <c r="G51" s="72"/>
       <c r="H51" s="10"/>
     </row>
     <row r="52" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
@@ -2809,61 +2806,61 @@
       <c r="B52" s="31" t="s">
         <v>68</v>
       </c>
-      <c r="C52" s="118"/>
-      <c r="D52" s="118"/>
-      <c r="E52" s="118"/>
-      <c r="F52" s="118"/>
-      <c r="G52" s="118"/>
+      <c r="C52" s="73"/>
+      <c r="D52" s="73"/>
+      <c r="E52" s="73"/>
+      <c r="F52" s="73"/>
+      <c r="G52" s="73"/>
       <c r="H52" s="10"/>
     </row>
     <row r="53" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="10"/>
-      <c r="B53" s="119"/>
-      <c r="C53" s="119"/>
-      <c r="D53" s="119"/>
-      <c r="E53" s="119"/>
-      <c r="F53" s="119"/>
-      <c r="G53" s="119"/>
+      <c r="B53" s="74"/>
+      <c r="C53" s="74"/>
+      <c r="D53" s="74"/>
+      <c r="E53" s="74"/>
+      <c r="F53" s="74"/>
+      <c r="G53" s="74"/>
       <c r="H53" s="10"/>
     </row>
     <row r="54" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="10"/>
-      <c r="B54" s="119"/>
-      <c r="C54" s="119"/>
-      <c r="D54" s="119"/>
-      <c r="E54" s="119"/>
-      <c r="F54" s="119"/>
-      <c r="G54" s="119"/>
+      <c r="B54" s="74"/>
+      <c r="C54" s="74"/>
+      <c r="D54" s="74"/>
+      <c r="E54" s="74"/>
+      <c r="F54" s="74"/>
+      <c r="G54" s="74"/>
       <c r="H54" s="10"/>
     </row>
     <row r="55" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="10"/>
-      <c r="B55" s="120"/>
-      <c r="C55" s="120"/>
-      <c r="D55" s="120"/>
-      <c r="E55" s="120"/>
-      <c r="F55" s="120"/>
-      <c r="G55" s="120"/>
+      <c r="B55" s="75"/>
+      <c r="C55" s="75"/>
+      <c r="D55" s="75"/>
+      <c r="E55" s="75"/>
+      <c r="F55" s="75"/>
+      <c r="G55" s="75"/>
       <c r="H55" s="10"/>
     </row>
     <row r="56" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="21"/>
-      <c r="B56" s="103" t="s">
+      <c r="B56" s="46" t="s">
         <v>69</v>
       </c>
-      <c r="C56" s="103"/>
-      <c r="D56" s="103"/>
-      <c r="E56" s="103"/>
-      <c r="F56" s="103"/>
-      <c r="G56" s="103"/>
+      <c r="C56" s="46"/>
+      <c r="D56" s="46"/>
+      <c r="E56" s="46"/>
+      <c r="F56" s="46"/>
+      <c r="G56" s="46"/>
       <c r="H56" s="22"/>
     </row>
     <row r="57" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="22"/>
-      <c r="B57" s="122" t="s">
+      <c r="B57" s="45" t="s">
         <v>70</v>
       </c>
-      <c r="C57" s="122"/>
+      <c r="C57" s="45"/>
       <c r="D57" s="32">
         <v>6</v>
       </c>
@@ -2876,76 +2873,76 @@
     </row>
     <row r="58" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="21"/>
-      <c r="B58" s="103" t="s">
+      <c r="B58" s="46" t="s">
         <v>72</v>
       </c>
-      <c r="C58" s="103"/>
-      <c r="D58" s="103"/>
-      <c r="E58" s="103"/>
-      <c r="F58" s="103"/>
-      <c r="G58" s="103"/>
+      <c r="C58" s="46"/>
+      <c r="D58" s="46"/>
+      <c r="E58" s="46"/>
+      <c r="F58" s="46"/>
+      <c r="G58" s="46"/>
       <c r="H58" s="22"/>
     </row>
     <row r="59" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="22"/>
-      <c r="B59" s="123" t="s">
+      <c r="B59" s="47" t="s">
         <v>73</v>
       </c>
-      <c r="C59" s="123"/>
+      <c r="C59" s="47"/>
       <c r="D59" s="34">
         <f>C61+C62+C64</f>
         <v>0</v>
       </c>
-      <c r="E59" s="124" t="s">
+      <c r="E59" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F59" s="124"/>
+      <c r="F59" s="48"/>
       <c r="G59" s="20"/>
       <c r="H59" s="22"/>
     </row>
     <row r="60" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="21"/>
-      <c r="B60" s="103" t="s">
+      <c r="B60" s="46" t="s">
         <v>75</v>
       </c>
-      <c r="C60" s="103"/>
-      <c r="D60" s="103"/>
-      <c r="E60" s="103"/>
-      <c r="F60" s="103"/>
-      <c r="G60" s="103"/>
+      <c r="C60" s="46"/>
+      <c r="D60" s="46"/>
+      <c r="E60" s="46"/>
+      <c r="F60" s="46"/>
+      <c r="G60" s="46"/>
       <c r="H60" s="22"/>
     </row>
     <row r="61" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="22"/>
       <c r="B61" s="33" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C61" s="35"/>
-      <c r="D61" s="125" t="s">
-        <v>89</v>
-      </c>
-      <c r="E61" s="126"/>
-      <c r="F61" s="126"/>
+      <c r="D61" s="49" t="s">
+        <v>88</v>
+      </c>
+      <c r="E61" s="50"/>
+      <c r="F61" s="50"/>
       <c r="G61" s="36">
         <f ca="1">E17</f>
-        <v>45973</v>
+        <v>46163</v>
       </c>
       <c r="H61" s="22"/>
     </row>
     <row r="62" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="22"/>
       <c r="B62" s="33" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C62" s="37"/>
-      <c r="D62" s="126" t="s">
+      <c r="D62" s="50" t="s">
         <v>76</v>
       </c>
-      <c r="E62" s="126"/>
-      <c r="F62" s="126"/>
+      <c r="E62" s="50"/>
+      <c r="F62" s="50"/>
       <c r="G62" s="36">
         <f ca="1">E17+7</f>
-        <v>45980</v>
+        <v>46170</v>
       </c>
       <c r="H62" s="38" t="s">
         <v>77</v>
@@ -2954,17 +2951,17 @@
     <row r="63" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="22"/>
       <c r="B63" s="33" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C63" s="37"/>
-      <c r="D63" s="127" t="s">
+      <c r="D63" s="51" t="s">
         <v>78</v>
       </c>
-      <c r="E63" s="127"/>
-      <c r="F63" s="127"/>
+      <c r="E63" s="51"/>
+      <c r="F63" s="51"/>
       <c r="G63" s="36">
         <f ca="1">E17+12</f>
-        <v>45985</v>
+        <v>46175</v>
       </c>
       <c r="H63" s="38" t="s">
         <v>77</v>
@@ -2973,17 +2970,17 @@
     <row r="64" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="22"/>
       <c r="B64" s="33" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C64" s="37"/>
-      <c r="D64" s="126" t="s">
+      <c r="D64" s="50" t="s">
         <v>79</v>
       </c>
-      <c r="E64" s="126"/>
-      <c r="F64" s="126"/>
+      <c r="E64" s="50"/>
+      <c r="F64" s="50"/>
       <c r="G64" s="36">
         <f ca="1">+G62+26</f>
-        <v>46006</v>
+        <v>46196</v>
       </c>
       <c r="H64" s="38" t="s">
         <v>77</v>
@@ -2991,77 +2988,75 @@
     </row>
     <row r="65" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="10"/>
-      <c r="B65" s="128" t="s">
+      <c r="B65" s="52" t="s">
         <v>80</v>
       </c>
-      <c r="C65" s="128"/>
-      <c r="D65" s="128"/>
-      <c r="E65" s="128"/>
-      <c r="F65" s="128"/>
-      <c r="G65" s="128"/>
+      <c r="C65" s="52"/>
+      <c r="D65" s="52"/>
+      <c r="E65" s="52"/>
+      <c r="F65" s="52"/>
+      <c r="G65" s="52"/>
       <c r="H65" s="39"/>
     </row>
     <row r="66" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="40" t="s">
         <v>81</v>
       </c>
-      <c r="B66" s="129" t="s">
+      <c r="B66" s="53" t="s">
         <v>82</v>
       </c>
-      <c r="C66" s="129"/>
-      <c r="D66" s="129"/>
-      <c r="E66" s="129"/>
-      <c r="F66" s="129"/>
-      <c r="G66" s="129"/>
+      <c r="C66" s="53"/>
+      <c r="D66" s="53"/>
+      <c r="E66" s="53"/>
+      <c r="F66" s="53"/>
+      <c r="G66" s="53"/>
     </row>
     <row r="67" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B67" s="121" t="s">
-        <v>94</v>
-      </c>
-      <c r="C67" s="121"/>
-      <c r="D67" s="121"/>
-      <c r="E67" s="121"/>
-      <c r="F67" s="121" t="s">
+      <c r="B67" s="44" t="s">
+        <v>93</v>
+      </c>
+      <c r="C67" s="44"/>
+      <c r="D67" s="44"/>
+      <c r="E67" s="44"/>
+      <c r="F67" s="44" t="s">
         <v>83</v>
       </c>
-      <c r="G67" s="121"/>
-      <c r="H67" s="121"/>
+      <c r="G67" s="44"/>
+      <c r="H67" s="44"/>
     </row>
     <row r="68" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B68" s="130" t="s">
+      <c r="B68" s="43" t="s">
         <v>84</v>
       </c>
-      <c r="C68" s="130"/>
-      <c r="D68" s="130"/>
-      <c r="E68" s="130"/>
-      <c r="F68" s="121" t="s">
+      <c r="C68" s="43"/>
+      <c r="D68" s="43"/>
+      <c r="E68" s="43"/>
+      <c r="F68" s="44" t="s">
         <v>85</v>
       </c>
-      <c r="G68" s="121"/>
-      <c r="H68" s="121"/>
+      <c r="G68" s="44"/>
+      <c r="H68" s="44"/>
     </row>
     <row r="69" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B69" s="130" t="s">
+      <c r="B69" s="43" t="s">
         <v>86</v>
       </c>
-      <c r="C69" s="130"/>
-      <c r="D69" s="130"/>
-      <c r="E69" s="130"/>
-      <c r="F69" s="121" t="s">
+      <c r="C69" s="43"/>
+      <c r="D69" s="43"/>
+      <c r="E69" s="43"/>
+      <c r="F69" s="44" t="s">
         <v>87</v>
       </c>
-      <c r="G69" s="121"/>
-      <c r="H69" s="121"/>
+      <c r="G69" s="44"/>
+      <c r="H69" s="44"/>
     </row>
     <row r="70" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B70" s="121" t="s">
-        <v>88</v>
-      </c>
-      <c r="C70" s="121"/>
-      <c r="D70" s="121"/>
-      <c r="E70" s="121"/>
-      <c r="F70" s="121"/>
-      <c r="G70" s="121"/>
+      <c r="B70" s="44"/>
+      <c r="C70" s="44"/>
+      <c r="D70" s="44"/>
+      <c r="E70" s="44"/>
+      <c r="F70" s="44"/>
+      <c r="G70" s="44"/>
     </row>
     <row r="71" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B71" s="41"/>
@@ -3089,51 +3084,37 @@
     <protectedRange algorithmName="SHA-512" hashValue="1IwEtpPovyRjspz9ti3J5udl070IPZ9gDlGmM3ZH/lFyQlLVVL2qbaMds7kHvZZkPq7VvowLV2MqpNnf8owpjQ==" saltValue="SwYyjj//I75seGLqQP0hyQ==" spinCount="100000" sqref="E37:G38 E39" name="Rango2_2"/>
   </protectedRanges>
   <mergeCells count="91">
-    <mergeCell ref="B68:E68"/>
-    <mergeCell ref="F68:H68"/>
-    <mergeCell ref="B69:E69"/>
-    <mergeCell ref="F69:H69"/>
-    <mergeCell ref="B70:E70"/>
-    <mergeCell ref="F70:G70"/>
-    <mergeCell ref="B67:E67"/>
-    <mergeCell ref="F67:H67"/>
-    <mergeCell ref="B57:C57"/>
-    <mergeCell ref="B58:G58"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="E59:F59"/>
-    <mergeCell ref="B60:G60"/>
-    <mergeCell ref="D61:F61"/>
-    <mergeCell ref="D62:F62"/>
-    <mergeCell ref="D63:F63"/>
-    <mergeCell ref="D64:F64"/>
-    <mergeCell ref="B65:G65"/>
-    <mergeCell ref="B66:G66"/>
-    <mergeCell ref="B56:G56"/>
-    <mergeCell ref="B43:D43"/>
-    <mergeCell ref="B44:G44"/>
-    <mergeCell ref="B45:D47"/>
-    <mergeCell ref="E45:G46"/>
-    <mergeCell ref="E47:G48"/>
-    <mergeCell ref="B48:D49"/>
-    <mergeCell ref="E49:G50"/>
-    <mergeCell ref="B50:D50"/>
-    <mergeCell ref="B51:G51"/>
-    <mergeCell ref="C52:G52"/>
-    <mergeCell ref="B53:G53"/>
-    <mergeCell ref="B54:G54"/>
-    <mergeCell ref="B55:G55"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="E40:G40"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="E41:G41"/>
-    <mergeCell ref="B42:D42"/>
-    <mergeCell ref="E42:G42"/>
-    <mergeCell ref="B37:D37"/>
-    <mergeCell ref="E37:G37"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="E38:G38"/>
-    <mergeCell ref="B39:D39"/>
-    <mergeCell ref="E39:G39"/>
+    <mergeCell ref="B9:G10"/>
+    <mergeCell ref="D4:F4"/>
+    <mergeCell ref="D5:F5"/>
+    <mergeCell ref="D6:F6"/>
+    <mergeCell ref="D7:F7"/>
+    <mergeCell ref="A8:H8"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="E21:G21"/>
+    <mergeCell ref="B11:E11"/>
+    <mergeCell ref="B12:G12"/>
+    <mergeCell ref="B13:G13"/>
+    <mergeCell ref="B15:E15"/>
+    <mergeCell ref="B16:E16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B18:G18"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="E19:G19"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="E20:G20"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="E22:G22"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="E23:G23"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="E24:G24"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="E25:G25"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="E26:G26"/>
+    <mergeCell ref="B27:D27"/>
+    <mergeCell ref="E27:G27"/>
     <mergeCell ref="B35:D36"/>
     <mergeCell ref="E35:G35"/>
     <mergeCell ref="E36:G36"/>
@@ -3149,44 +3130,58 @@
     <mergeCell ref="E33:G33"/>
     <mergeCell ref="B34:D34"/>
     <mergeCell ref="E34:G34"/>
-    <mergeCell ref="B25:D25"/>
-    <mergeCell ref="E25:G25"/>
-    <mergeCell ref="B26:D26"/>
-    <mergeCell ref="E26:G26"/>
-    <mergeCell ref="B27:D27"/>
-    <mergeCell ref="E27:G27"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="E22:G22"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="E23:G23"/>
-    <mergeCell ref="B24:D24"/>
-    <mergeCell ref="E24:G24"/>
-    <mergeCell ref="B21:D21"/>
-    <mergeCell ref="E21:G21"/>
-    <mergeCell ref="B11:E11"/>
-    <mergeCell ref="B12:G12"/>
-    <mergeCell ref="B13:G13"/>
-    <mergeCell ref="B15:E15"/>
-    <mergeCell ref="B16:E16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B18:G18"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="E19:G19"/>
-    <mergeCell ref="B20:D20"/>
-    <mergeCell ref="E20:G20"/>
-    <mergeCell ref="B9:G10"/>
-    <mergeCell ref="D4:F4"/>
-    <mergeCell ref="D5:F5"/>
-    <mergeCell ref="D6:F6"/>
-    <mergeCell ref="D7:F7"/>
-    <mergeCell ref="A8:H8"/>
+    <mergeCell ref="B37:D37"/>
+    <mergeCell ref="E37:G37"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="E38:G38"/>
+    <mergeCell ref="B39:D39"/>
+    <mergeCell ref="E39:G39"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="E40:G40"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="E41:G41"/>
+    <mergeCell ref="B42:D42"/>
+    <mergeCell ref="E42:G42"/>
+    <mergeCell ref="B56:G56"/>
+    <mergeCell ref="B43:D43"/>
+    <mergeCell ref="B44:G44"/>
+    <mergeCell ref="B45:D47"/>
+    <mergeCell ref="E45:G46"/>
+    <mergeCell ref="E47:G48"/>
+    <mergeCell ref="B48:D49"/>
+    <mergeCell ref="E49:G50"/>
+    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="B51:G51"/>
+    <mergeCell ref="C52:G52"/>
+    <mergeCell ref="B53:G53"/>
+    <mergeCell ref="B54:G54"/>
+    <mergeCell ref="B55:G55"/>
+    <mergeCell ref="B67:E67"/>
+    <mergeCell ref="F67:H67"/>
+    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="B58:G58"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="E59:F59"/>
+    <mergeCell ref="B60:G60"/>
+    <mergeCell ref="D61:F61"/>
+    <mergeCell ref="D62:F62"/>
+    <mergeCell ref="D63:F63"/>
+    <mergeCell ref="D64:F64"/>
+    <mergeCell ref="B65:G65"/>
+    <mergeCell ref="B66:G66"/>
+    <mergeCell ref="B68:E68"/>
+    <mergeCell ref="F68:H68"/>
+    <mergeCell ref="B69:E69"/>
+    <mergeCell ref="F69:H69"/>
+    <mergeCell ref="B70:E70"/>
+    <mergeCell ref="F70:G70"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="D7" r:id="rId1" display="https://www.planosperu.com.pe" xr:uid="{506D083F-F460-4953-991A-891366CADB27}"/>
   </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.59055118110236227" right="0.59055118110236227" top="0.59055118110236227" bottom="0" header="0" footer="0"/>
-  <pageSetup paperSize="9" scale="90" orientation="portrait" r:id="rId2"/>
+  <pageSetup paperSize="9" scale="89" orientation="portrait" r:id="rId2"/>
   <drawing r:id="rId3"/>
 </worksheet>
 </file>